--- a/Deliverables/BOM/Fob_Transmitter/Client_BOM_Fob_Transmitter.xlsx
+++ b/Deliverables/BOM/Fob_Transmitter/Client_BOM_Fob_Transmitter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8968B353-47E0-4036-97B3-51D229C685AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8B308D-B550-4F38-B7A9-0628348339CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="213">
   <si>
     <t>Component list</t>
   </si>
@@ -666,6 +666,9 @@
   </si>
   <si>
     <t>[Fob_Transmitter]</t>
+  </si>
+  <si>
+    <t>Quantity (5 Boards)</t>
   </si>
 </sst>
 </file>
@@ -677,7 +680,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,15 +841,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -880,7 +874,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1114,21 +1108,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1155,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1316,52 +1295,28 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1386,7 +1341,7 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1421,13 +1376,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -1735,7 +1690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1748,15 +1703,16 @@
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1766,15 +1722,16 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="77"/>
-    </row>
-    <row r="2" spans="1:23" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="69"/>
+    </row>
+    <row r="2" spans="1:24" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="39"/>
@@ -1794,9 +1751,10 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="40"/>
@@ -1816,9 +1774,10 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="78"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P3" s="5"/>
+      <c r="Q3" s="70"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="40"/>
@@ -1838,9 +1797,10 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
-      <c r="P4" s="79"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="71"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="40"/>
@@ -1860,9 +1820,10 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="79"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P5" s="6"/>
+      <c r="Q5" s="71"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="41"/>
@@ -1878,9 +1839,10 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="79"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P6" s="6"/>
+      <c r="Q6" s="71"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="42"/>
@@ -1896,9 +1858,10 @@
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="79"/>
-    </row>
-    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="8"/>
+      <c r="Q7" s="71"/>
+    </row>
+    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="43"/>
@@ -1914,9 +1877,10 @@
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
-      <c r="P8" s="79"/>
-    </row>
-    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="71"/>
+    </row>
+    <row r="9" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -1949,22 +1913,25 @@
         <v>179</v>
       </c>
       <c r="L9" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="O9" s="32" t="s">
+      <c r="P9" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="P9" s="32" t="s">
+      <c r="Q9" s="32" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="38">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1997,25 +1964,29 @@
       <c r="K10" s="46">
         <v>7</v>
       </c>
-      <c r="L10" s="46">
+      <c r="L10" s="47">
+        <f>K10*5</f>
+        <v>35</v>
+      </c>
+      <c r="M10" s="46">
         <v>100</v>
       </c>
-      <c r="M10" s="52">
+      <c r="N10" s="52">
         <v>8.6000000000000007E-2</v>
       </c>
-      <c r="N10" s="52">
-        <f>M10*L10</f>
+      <c r="O10" s="52">
+        <f t="shared" ref="O10:O26" si="0">N10*M10</f>
         <v>8.6000000000000014</v>
       </c>
-      <c r="O10" s="48"/>
-      <c r="P10" s="52"/>
-      <c r="T10" s="74"/>
-      <c r="W10" s="75"/>
-    </row>
-    <row r="11" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P10" s="48"/>
+      <c r="Q10" s="52"/>
+      <c r="U10" s="65"/>
+      <c r="X10" s="66"/>
+    </row>
+    <row r="11" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
-        <f t="shared" ref="B11:B47" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B47" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="59" t="s">
@@ -2045,22 +2016,26 @@
       <c r="K11" s="49">
         <v>2</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="50">
+        <f t="shared" ref="L11:L47" si="2">K11*5</f>
+        <v>10</v>
+      </c>
+      <c r="M11" s="49">
         <v>20</v>
       </c>
-      <c r="M11" s="53">
+      <c r="N11" s="53">
         <v>0.1129</v>
       </c>
-      <c r="N11" s="53">
-        <f>M11*L11</f>
+      <c r="O11" s="53">
+        <f t="shared" si="0"/>
         <v>2.258</v>
       </c>
-      <c r="O11" s="51"/>
-      <c r="P11" s="53"/>
-      <c r="T11" s="74"/>
-      <c r="W11" s="75"/>
-    </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P11" s="51"/>
+      <c r="Q11" s="53"/>
+      <c r="U11" s="65"/>
+      <c r="X11" s="66"/>
+    </row>
+    <row r="12" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2093,790 +2068,862 @@
       <c r="K12" s="46">
         <v>1</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M12" s="46">
         <v>50</v>
       </c>
-      <c r="M12" s="52">
+      <c r="N12" s="52">
         <v>8.4199999999999997E-2</v>
       </c>
-      <c r="N12" s="52">
-        <f>M12*L12</f>
+      <c r="O12" s="52">
+        <f t="shared" si="0"/>
         <v>4.21</v>
       </c>
-      <c r="O12" s="48"/>
-      <c r="P12" s="52"/>
-      <c r="T12" s="74"/>
-      <c r="W12" s="75"/>
-    </row>
-    <row r="13" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P12" s="48"/>
+      <c r="Q12" s="52"/>
+      <c r="U12" s="65"/>
+      <c r="X12" s="66"/>
+    </row>
+    <row r="13" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
         <f>ROW(B13) - ROW($B$9)</f>
         <v>4</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="I13" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J13" s="47" t="s">
+      <c r="I13" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J13" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="49">
         <v>1</v>
       </c>
-      <c r="L13" s="46">
+      <c r="L13" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M13" s="49">
         <v>20</v>
       </c>
-      <c r="M13" s="52">
+      <c r="N13" s="53">
         <v>0.1069</v>
       </c>
-      <c r="N13" s="52">
-        <f>M13*L13</f>
+      <c r="O13" s="53">
+        <f t="shared" si="0"/>
         <v>2.1379999999999999</v>
       </c>
-      <c r="O13" s="48"/>
-      <c r="P13" s="52"/>
-      <c r="T13" s="74"/>
-      <c r="W13" s="75"/>
-    </row>
-    <row r="14" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="51"/>
+      <c r="Q13" s="53"/>
+      <c r="U13" s="65"/>
+      <c r="X13" s="66"/>
+    </row>
+    <row r="14" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="K14" s="46">
+        <v>1</v>
+      </c>
+      <c r="L14" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M14" s="46">
+        <v>50</v>
+      </c>
+      <c r="N14" s="52">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="O14" s="52">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J14" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="K14" s="49">
-        <v>1</v>
-      </c>
-      <c r="L14" s="49">
-        <v>50</v>
-      </c>
-      <c r="M14" s="53">
-        <v>8.5699999999999998E-2</v>
-      </c>
-      <c r="N14" s="53">
-        <f>M14*L14</f>
         <v>4.2850000000000001</v>
       </c>
-      <c r="O14" s="51"/>
-      <c r="P14" s="53"/>
-      <c r="T14" s="74"/>
-      <c r="W14" s="75"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P14" s="48"/>
+      <c r="Q14" s="52"/>
+      <c r="U14" s="65"/>
+      <c r="X14" s="66"/>
+    </row>
+    <row r="15" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="38">
         <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="I15" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J15" s="47" t="s">
+      <c r="I15" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J15" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="49">
         <v>2</v>
       </c>
-      <c r="L15" s="46">
+      <c r="L15" s="50">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="49">
         <v>50</v>
       </c>
-      <c r="M15" s="52">
+      <c r="N15" s="53">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="N15" s="52">
-        <f>M15*L15</f>
+      <c r="O15" s="53">
+        <f t="shared" si="0"/>
         <v>4.3999999999999995</v>
       </c>
-      <c r="O15" s="48"/>
-      <c r="P15" s="52"/>
-      <c r="T15" s="74"/>
-      <c r="W15" s="75"/>
-    </row>
-    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P15" s="51"/>
+      <c r="Q15" s="53"/>
+      <c r="U15" s="65"/>
+      <c r="X15" s="66"/>
+    </row>
+    <row r="16" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="46">
+        <v>1</v>
+      </c>
+      <c r="L16" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M16" s="46">
+        <v>100</v>
+      </c>
+      <c r="N16" s="52">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="O16" s="52">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J16" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="K16" s="49">
-        <v>1</v>
-      </c>
-      <c r="L16" s="49">
-        <v>100</v>
-      </c>
-      <c r="M16" s="53">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="N16" s="53">
-        <f>M16*L16</f>
         <v>8.3000000000000007</v>
       </c>
-      <c r="O16" s="51"/>
-      <c r="P16" s="53"/>
-      <c r="T16" s="74"/>
-      <c r="W16" s="75"/>
-    </row>
-    <row r="17" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P16" s="48"/>
+      <c r="Q16" s="52"/>
+      <c r="U16" s="65"/>
+      <c r="X16" s="66"/>
+    </row>
+    <row r="17" spans="1:24" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="38">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="I17" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" s="47" t="s">
+      <c r="I17" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="49">
         <v>1</v>
       </c>
-      <c r="L17" s="46"/>
-      <c r="M17" s="52">
-        <v>0.08</v>
-      </c>
-      <c r="N17" s="52">
-        <f>M17*L17</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="70"/>
-      <c r="P17" s="52"/>
-      <c r="T17" s="74"/>
-      <c r="W17" s="75"/>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M17" s="49">
+        <v>7</v>
+      </c>
+      <c r="N17" s="53">
+        <v>1.24</v>
+      </c>
+      <c r="O17" s="53">
+        <f t="shared" si="0"/>
+        <v>8.68</v>
+      </c>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="53"/>
+      <c r="U17" s="65"/>
+      <c r="X17" s="66"/>
+    </row>
+    <row r="18" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="49" t="s">
+      <c r="F18" s="46" t="s">
         <v>83</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="49" t="s">
+      <c r="H18" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="J18" s="50" t="s">
+      <c r="J18" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="K18" s="49">
+      <c r="K18" s="46">
         <v>1</v>
       </c>
-      <c r="L18" s="49">
+      <c r="L18" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M18" s="46">
         <v>50</v>
       </c>
-      <c r="M18" s="53">
+      <c r="N18" s="52">
         <v>8.8900000000000007E-2</v>
       </c>
-      <c r="N18" s="53">
-        <f>M18*L18</f>
+      <c r="O18" s="52">
+        <f t="shared" si="0"/>
         <v>4.4450000000000003</v>
       </c>
-      <c r="O18" s="51"/>
-      <c r="P18" s="53"/>
-      <c r="T18" s="74"/>
-      <c r="W18" s="75"/>
-    </row>
-    <row r="19" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P18" s="48"/>
+      <c r="Q18" s="52"/>
+      <c r="U18" s="65"/>
+      <c r="X18" s="66"/>
+    </row>
+    <row r="19" spans="1:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E19" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G19" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="I19" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J19" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="K19" s="46">
+      <c r="I19" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J19" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K19" s="49">
         <v>12</v>
       </c>
-      <c r="L19" s="46">
+      <c r="L19" s="50">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M19" s="49">
         <v>80</v>
       </c>
-      <c r="M19" s="52">
+      <c r="N19" s="53">
         <v>0.10580000000000001</v>
       </c>
-      <c r="N19" s="52">
-        <f>M19*L19</f>
+      <c r="O19" s="53">
+        <f t="shared" si="0"/>
         <v>8.4640000000000004</v>
       </c>
-      <c r="O19" s="48"/>
-      <c r="P19" s="52"/>
-      <c r="T19" s="74"/>
-      <c r="W19" s="75"/>
-    </row>
-    <row r="20" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P19" s="51"/>
+      <c r="Q19" s="53"/>
+      <c r="U19" s="65"/>
+      <c r="X19" s="66"/>
+    </row>
+    <row r="20" spans="1:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" s="46">
+        <v>1</v>
+      </c>
+      <c r="L20" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M20" s="46">
+        <v>10</v>
+      </c>
+      <c r="N20" s="52">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="O20" s="52">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="I20" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J20" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="49">
-        <v>1</v>
-      </c>
-      <c r="L20" s="49">
-        <v>10</v>
-      </c>
-      <c r="M20" s="53">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="N20" s="53">
-        <f>M20*L20</f>
         <v>1.32</v>
       </c>
-      <c r="O20" s="51"/>
-      <c r="P20" s="53"/>
-      <c r="T20" s="74"/>
-      <c r="W20" s="75"/>
-    </row>
-    <row r="21" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P20" s="48"/>
+      <c r="Q20" s="52"/>
+      <c r="U20" s="65"/>
+      <c r="X20" s="66"/>
+    </row>
+    <row r="21" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="46" t="s">
+      <c r="F21" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="I21" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J21" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="K21" s="46">
+      <c r="I21" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K21" s="49">
         <v>1</v>
       </c>
-      <c r="L21" s="46">
+      <c r="L21" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M21" s="49">
         <v>20</v>
       </c>
-      <c r="M21" s="52">
+      <c r="N21" s="53">
         <v>0.1065</v>
       </c>
-      <c r="N21" s="52">
-        <f>M21*L21</f>
+      <c r="O21" s="53">
+        <f t="shared" si="0"/>
         <v>2.13</v>
       </c>
-      <c r="O21" s="48"/>
-      <c r="P21" s="52"/>
-      <c r="T21" s="74"/>
-      <c r="W21" s="75"/>
-    </row>
-    <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P21" s="51"/>
+      <c r="Q21" s="53"/>
+      <c r="U21" s="65"/>
+      <c r="X21" s="66"/>
+    </row>
+    <row r="22" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J22" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="K22" s="46">
+        <v>1</v>
+      </c>
+      <c r="L22" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M22" s="46">
+        <v>10</v>
+      </c>
+      <c r="N22" s="52">
+        <v>0.1696</v>
+      </c>
+      <c r="O22" s="52">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="G22" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J22" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="K22" s="49">
-        <v>1</v>
-      </c>
-      <c r="L22" s="49">
-        <v>10</v>
-      </c>
-      <c r="M22" s="53">
-        <v>0.1696</v>
-      </c>
-      <c r="N22" s="53">
-        <f>M22*L22</f>
         <v>1.696</v>
       </c>
-      <c r="O22" s="51"/>
-      <c r="P22" s="53"/>
-      <c r="T22" s="74"/>
-      <c r="W22" s="75"/>
-    </row>
-    <row r="23" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P22" s="48"/>
+      <c r="Q22" s="52"/>
+      <c r="U22" s="65"/>
+      <c r="X22" s="66"/>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G23" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="H23" s="46" t="s">
+      <c r="H23" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="I23" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J23" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="K23" s="46">
+      <c r="I23" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K23" s="49">
         <v>1</v>
       </c>
-      <c r="L23" s="46">
+      <c r="L23" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M23" s="49">
         <v>50</v>
       </c>
-      <c r="M23" s="52">
+      <c r="N23" s="53">
         <v>9.4399999999999998E-2</v>
       </c>
-      <c r="N23" s="52">
-        <f>M23*L23</f>
+      <c r="O23" s="53">
+        <f t="shared" si="0"/>
         <v>4.72</v>
       </c>
-      <c r="O23" s="48"/>
-      <c r="P23" s="52"/>
-      <c r="T23" s="74"/>
-      <c r="W23" s="75"/>
-    </row>
-    <row r="24" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="51"/>
+      <c r="Q23" s="53"/>
+      <c r="U23" s="65"/>
+      <c r="X23" s="66"/>
+    </row>
+    <row r="24" spans="1:24" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="38">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="K24" s="46">
+        <v>1</v>
+      </c>
+      <c r="L24" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M24" s="46">
+        <v>7</v>
+      </c>
+      <c r="N24" s="52">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O24" s="52">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J24" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="K24" s="49">
-        <v>1</v>
-      </c>
-      <c r="L24" s="49"/>
-      <c r="M24" s="53">
-        <v>0.08</v>
-      </c>
-      <c r="N24" s="53">
-        <f>M24*L24</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="71"/>
-      <c r="P24" s="53"/>
-      <c r="T24" s="74"/>
-      <c r="W24" s="75"/>
-    </row>
-    <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="52"/>
+      <c r="U24" s="65"/>
+      <c r="X24" s="66"/>
+    </row>
+    <row r="25" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="38">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="I25" s="46" t="s">
+      <c r="I25" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="J25" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="K25" s="46">
+      <c r="J25" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K25" s="49">
         <v>1</v>
       </c>
-      <c r="L25" s="46">
+      <c r="L25" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M25" s="49">
         <v>100</v>
       </c>
-      <c r="M25" s="52">
+      <c r="N25" s="53">
         <v>8.7400000000000005E-2</v>
       </c>
-      <c r="N25" s="52">
-        <f>M25*L25</f>
+      <c r="O25" s="53">
+        <f t="shared" si="0"/>
         <v>8.74</v>
       </c>
-      <c r="O25" s="48"/>
-      <c r="P25" s="52"/>
-      <c r="T25" s="74"/>
-      <c r="W25" s="75"/>
-    </row>
-    <row r="26" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P25" s="51"/>
+      <c r="Q25" s="53"/>
+      <c r="U25" s="65"/>
+      <c r="X25" s="66"/>
+    </row>
+    <row r="26" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="47">
+        <v>61300211121</v>
+      </c>
+      <c r="H26" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="K26" s="46">
+        <v>1</v>
+      </c>
+      <c r="L26" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M26" s="46">
+        <v>50</v>
+      </c>
+      <c r="N26" s="52">
+        <v>9.4600000000000004E-2</v>
+      </c>
+      <c r="O26" s="52">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="61">
-        <v>61300211121</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J26" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" s="49">
-        <v>1</v>
-      </c>
-      <c r="L26" s="49">
-        <v>50</v>
-      </c>
-      <c r="M26" s="53">
-        <v>9.4600000000000004E-2</v>
-      </c>
-      <c r="N26" s="53">
-        <f>M26*L26</f>
         <v>4.7300000000000004</v>
       </c>
-      <c r="O26" s="51"/>
-      <c r="P26" s="53"/>
-      <c r="T26" s="74"/>
-      <c r="W26" s="75"/>
-    </row>
-    <row r="27" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P26" s="48"/>
+      <c r="Q26" s="52"/>
+      <c r="U26" s="65"/>
+      <c r="X26" s="66"/>
+    </row>
+    <row r="27" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="F27" s="46" t="s">
+      <c r="E27" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J27" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="K27" s="46">
+      <c r="H27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J27" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27" s="49">
         <v>1</v>
       </c>
-      <c r="L27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="M27" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="N27" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="O27" s="73" t="s">
+      <c r="L27" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="N27" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="O27" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="P27" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="P27" s="52"/>
-      <c r="T27" s="74"/>
-      <c r="W27" s="75"/>
-    </row>
-    <row r="28" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q27" s="53"/>
+      <c r="U27" s="65"/>
+      <c r="X27" s="66"/>
+    </row>
+    <row r="28" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="50" t="s">
+      <c r="G28" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J28" s="50" t="s">
+      <c r="I28" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J28" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="K28" s="49">
+      <c r="K28" s="46">
         <v>5</v>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="47">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="M28" s="46">
         <v>100</v>
       </c>
-      <c r="M28" s="53">
+      <c r="N28" s="52">
         <v>8.1699999999999995E-2</v>
       </c>
-      <c r="N28" s="53">
-        <f>M28*L28</f>
+      <c r="O28" s="52">
+        <f t="shared" ref="O28:O36" si="3">N28*M28</f>
         <v>8.17</v>
       </c>
-      <c r="O28" s="51"/>
-      <c r="P28" s="53"/>
-      <c r="T28" s="74"/>
-      <c r="W28" s="75"/>
-    </row>
-    <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P28" s="48"/>
+      <c r="Q28" s="52"/>
+      <c r="U28" s="65"/>
+      <c r="X28" s="66"/>
+    </row>
+    <row r="29" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C29" s="59" t="s">
@@ -2906,22 +2953,26 @@
       <c r="K29" s="49">
         <v>1</v>
       </c>
-      <c r="L29" s="49">
+      <c r="L29" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M29" s="49">
         <v>100</v>
       </c>
-      <c r="M29" s="53">
+      <c r="N29" s="53">
         <v>8.1500000000000003E-2</v>
       </c>
-      <c r="N29" s="53">
-        <f>M29*L29</f>
+      <c r="O29" s="53">
+        <f t="shared" si="3"/>
         <v>8.15</v>
       </c>
-      <c r="O29" s="51"/>
-      <c r="P29" s="53"/>
-      <c r="T29" s="74"/>
-      <c r="W29" s="75"/>
-    </row>
-    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P29" s="51"/>
+      <c r="Q29" s="53"/>
+      <c r="U29" s="65"/>
+      <c r="X29" s="66"/>
+    </row>
+    <row r="30" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -2954,25 +3005,29 @@
       <c r="K30" s="46">
         <v>1</v>
       </c>
-      <c r="L30" s="46">
+      <c r="L30" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M30" s="46">
         <v>100</v>
       </c>
-      <c r="M30" s="52">
+      <c r="N30" s="52">
         <v>8.1299999999999997E-2</v>
       </c>
-      <c r="N30" s="52">
-        <f>M30*L30</f>
+      <c r="O30" s="52">
+        <f t="shared" si="3"/>
         <v>8.129999999999999</v>
       </c>
-      <c r="O30" s="48"/>
-      <c r="P30" s="52"/>
-      <c r="T30" s="74"/>
-      <c r="W30" s="75"/>
-    </row>
-    <row r="31" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P30" s="48"/>
+      <c r="Q30" s="52"/>
+      <c r="U30" s="65"/>
+      <c r="X30" s="66"/>
+    </row>
+    <row r="31" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C31" s="59" t="s">
@@ -3002,22 +3057,26 @@
       <c r="K31" s="49">
         <v>4</v>
       </c>
-      <c r="L31" s="49">
+      <c r="L31" s="50">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M31" s="49">
         <v>100</v>
       </c>
-      <c r="M31" s="53">
+      <c r="N31" s="53">
         <v>8.14E-2</v>
       </c>
-      <c r="N31" s="53">
-        <f>M31*L31</f>
+      <c r="O31" s="53">
+        <f t="shared" si="3"/>
         <v>8.14</v>
       </c>
-      <c r="O31" s="51"/>
-      <c r="P31" s="53"/>
-      <c r="T31" s="74"/>
-      <c r="W31" s="75"/>
-    </row>
-    <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P31" s="51"/>
+      <c r="Q31" s="53"/>
+      <c r="U31" s="65"/>
+      <c r="X31" s="66"/>
+    </row>
+    <row r="32" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="38">
         <f>ROW(B32) - ROW($B$9)</f>
@@ -3050,25 +3109,29 @@
       <c r="K32" s="46">
         <v>1</v>
       </c>
-      <c r="L32" s="46">
+      <c r="L32" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M32" s="46">
         <v>100</v>
       </c>
-      <c r="M32" s="52">
+      <c r="N32" s="52">
         <v>8.14E-2</v>
       </c>
-      <c r="N32" s="52">
-        <f>M32*L32</f>
+      <c r="O32" s="52">
+        <f t="shared" si="3"/>
         <v>8.14</v>
       </c>
-      <c r="O32" s="48"/>
-      <c r="P32" s="52"/>
-      <c r="T32" s="74"/>
-      <c r="W32" s="75"/>
-    </row>
-    <row r="33" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P32" s="48"/>
+      <c r="Q32" s="52"/>
+      <c r="U32" s="65"/>
+      <c r="X32" s="66"/>
+    </row>
+    <row r="33" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="C33" s="59" t="s">
@@ -3098,22 +3161,26 @@
       <c r="K33" s="49">
         <v>1</v>
       </c>
-      <c r="L33" s="49">
+      <c r="L33" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M33" s="49">
         <v>100</v>
       </c>
-      <c r="M33" s="53">
+      <c r="N33" s="53">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="N33" s="53">
-        <f>M33*L33</f>
+      <c r="O33" s="53">
+        <f t="shared" si="3"/>
         <v>8.06</v>
       </c>
-      <c r="O33" s="51"/>
-      <c r="P33" s="53"/>
-      <c r="T33" s="74"/>
-      <c r="W33" s="75"/>
-    </row>
-    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P33" s="51"/>
+      <c r="Q33" s="53"/>
+      <c r="U33" s="65"/>
+      <c r="X33" s="66"/>
+    </row>
+    <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="38">
         <f>ROW(B34) - ROW($B$9)</f>
@@ -3146,70 +3213,78 @@
       <c r="K34" s="46">
         <v>1</v>
       </c>
-      <c r="L34" s="46">
+      <c r="L34" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M34" s="46">
         <v>100</v>
       </c>
-      <c r="M34" s="52">
+      <c r="N34" s="52">
         <v>8.1200000000000008E-2</v>
       </c>
-      <c r="N34" s="52">
-        <f>M34*L34</f>
+      <c r="O34" s="52">
+        <f t="shared" si="3"/>
         <v>8.120000000000001</v>
       </c>
-      <c r="O34" s="48"/>
-      <c r="P34" s="52"/>
-      <c r="T34" s="74"/>
-      <c r="W34" s="75"/>
-    </row>
-    <row r="35" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P34" s="48"/>
+      <c r="Q34" s="52"/>
+      <c r="U34" s="65"/>
+      <c r="X34" s="66"/>
+    </row>
+    <row r="35" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="59" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="E35" s="65" t="s">
+      <c r="E35" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="65" t="s">
+      <c r="G35" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="H35" s="64" t="s">
+      <c r="H35" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="I35" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="J35" s="65" t="s">
+      <c r="I35" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="K35" s="64">
+      <c r="K35" s="49">
         <v>1</v>
       </c>
-      <c r="L35" s="64">
+      <c r="L35" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M35" s="49">
         <v>100</v>
       </c>
-      <c r="M35" s="66">
+      <c r="N35" s="53">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="N35" s="66">
-        <f>M35*L35</f>
+      <c r="O35" s="53">
+        <f t="shared" si="3"/>
         <v>8.1</v>
       </c>
-      <c r="O35" s="67"/>
-      <c r="P35" s="66"/>
-      <c r="T35" s="74"/>
-      <c r="W35" s="75"/>
-    </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P35" s="51"/>
+      <c r="Q35" s="53"/>
+      <c r="U35" s="65"/>
+      <c r="X35" s="66"/>
+    </row>
+    <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="38">
         <f>ROW(B36) - ROW($B$9)</f>
@@ -3242,25 +3317,29 @@
       <c r="K36" s="46">
         <v>1</v>
       </c>
-      <c r="L36" s="46">
+      <c r="L36" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M36" s="46">
         <v>100</v>
       </c>
-      <c r="M36" s="52">
+      <c r="N36" s="52">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="N36" s="52">
-        <f>M36*L36</f>
+      <c r="O36" s="52">
+        <f t="shared" si="3"/>
         <v>8.1</v>
       </c>
-      <c r="O36" s="48"/>
-      <c r="P36" s="52"/>
-      <c r="T36" s="74"/>
-      <c r="W36" s="75"/>
-    </row>
-    <row r="37" spans="1:23" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P36" s="48"/>
+      <c r="Q36" s="52"/>
+      <c r="U36" s="65"/>
+      <c r="X36" s="66"/>
+    </row>
+    <row r="37" spans="1:24" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="C37" s="59" t="s">
@@ -3275,7 +3354,7 @@
       <c r="F37" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="50" t="s">
         <v>97</v>
       </c>
       <c r="H37" s="49" t="s">
@@ -3290,23 +3369,27 @@
       <c r="K37" s="49">
         <v>31</v>
       </c>
-      <c r="L37" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="M37" s="53" t="s">
+      <c r="L37" s="50">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+      <c r="M37" s="49" t="s">
         <v>194</v>
       </c>
       <c r="N37" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="O37" s="72" t="s">
+      <c r="O37" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="P37" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="P37" s="53"/>
-      <c r="T37" s="74"/>
-      <c r="W37" s="75"/>
-    </row>
-    <row r="38" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q37" s="53"/>
+      <c r="U37" s="65"/>
+      <c r="X37" s="66"/>
+    </row>
+    <row r="38" spans="1:24" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="38">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -3324,7 +3407,7 @@
       <c r="F38" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="47" t="s">
         <v>98</v>
       </c>
       <c r="H38" s="46" t="s">
@@ -3339,25 +3422,29 @@
       <c r="K38" s="46">
         <v>9</v>
       </c>
-      <c r="L38" s="46">
+      <c r="L38" s="47">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="M38" s="46">
         <v>50</v>
       </c>
-      <c r="M38" s="52">
+      <c r="N38" s="52">
         <v>0.14360000000000001</v>
       </c>
-      <c r="N38" s="52">
-        <f>M38*L38</f>
+      <c r="O38" s="52">
+        <f t="shared" ref="O38:O47" si="4">N38*M38</f>
         <v>7.1800000000000006</v>
       </c>
-      <c r="O38" s="48"/>
-      <c r="P38" s="52"/>
-      <c r="T38" s="74"/>
-      <c r="W38" s="75"/>
-    </row>
-    <row r="39" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P38" s="48"/>
+      <c r="Q38" s="52"/>
+      <c r="U38" s="65"/>
+      <c r="X38" s="66"/>
+    </row>
+    <row r="39" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C39" s="59" t="s">
@@ -3387,22 +3474,26 @@
       <c r="K39" s="49">
         <v>1</v>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M39" s="49">
         <v>6</v>
       </c>
-      <c r="M39" s="53">
+      <c r="N39" s="53">
         <v>0.5534</v>
       </c>
-      <c r="N39" s="53">
-        <f>M39*L39</f>
+      <c r="O39" s="53">
+        <f t="shared" si="4"/>
         <v>3.3204000000000002</v>
       </c>
-      <c r="O39" s="51"/>
-      <c r="P39" s="53"/>
-      <c r="T39" s="74"/>
-      <c r="W39" s="75"/>
-    </row>
-    <row r="40" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P39" s="51"/>
+      <c r="Q39" s="53"/>
+      <c r="U39" s="65"/>
+      <c r="X39" s="66"/>
+    </row>
+    <row r="40" spans="1:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="38">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -3435,25 +3526,29 @@
       <c r="K40" s="46">
         <v>1</v>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M40" s="46">
         <v>6</v>
       </c>
-      <c r="M40" s="52">
+      <c r="N40" s="52">
         <v>0.86669999999999991</v>
       </c>
-      <c r="N40" s="52">
-        <f>M40*L40</f>
+      <c r="O40" s="52">
+        <f t="shared" si="4"/>
         <v>5.2001999999999997</v>
       </c>
-      <c r="O40" s="48"/>
-      <c r="P40" s="52"/>
-      <c r="T40" s="74"/>
-      <c r="W40" s="75"/>
-    </row>
-    <row r="41" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P40" s="48"/>
+      <c r="Q40" s="52"/>
+      <c r="U40" s="65"/>
+      <c r="X40" s="66"/>
+    </row>
+    <row r="41" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="C41" s="59" t="s">
@@ -3483,22 +3578,26 @@
       <c r="K41" s="49">
         <v>1</v>
       </c>
-      <c r="L41" s="49">
+      <c r="L41" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M41" s="49">
         <v>6</v>
       </c>
-      <c r="M41" s="53">
+      <c r="N41" s="53">
         <v>1.0370999999999999</v>
       </c>
-      <c r="N41" s="53">
-        <f>M41*L41</f>
+      <c r="O41" s="53">
+        <f t="shared" si="4"/>
         <v>6.2225999999999999</v>
       </c>
-      <c r="O41" s="51"/>
-      <c r="P41" s="53"/>
-      <c r="T41" s="74"/>
-      <c r="W41" s="75"/>
-    </row>
-    <row r="42" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P41" s="51"/>
+      <c r="Q41" s="53"/>
+      <c r="U41" s="65"/>
+      <c r="X41" s="66"/>
+    </row>
+    <row r="42" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -3525,27 +3624,35 @@
       <c r="I42" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="J42" s="47"/>
+      <c r="J42" s="47" t="s">
+        <v>194</v>
+      </c>
       <c r="K42" s="46">
         <v>1</v>
       </c>
-      <c r="L42" s="46"/>
-      <c r="M42" s="52">
-        <v>0.08</v>
+      <c r="L42" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M42" s="46">
+        <v>6</v>
       </c>
       <c r="N42" s="52">
-        <f>M42*L42</f>
-        <v>0</v>
-      </c>
-      <c r="O42" s="70"/>
-      <c r="P42" s="52"/>
-      <c r="T42" s="74"/>
-      <c r="W42" s="75"/>
-    </row>
-    <row r="43" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="O42" s="52">
+        <f t="shared" si="4"/>
+        <v>13.559999999999999</v>
+      </c>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="52"/>
+      <c r="U42" s="65"/>
+      <c r="X42" s="66"/>
+    </row>
+    <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="C43" s="59" t="s">
@@ -3575,22 +3682,26 @@
       <c r="K43" s="49">
         <v>1</v>
       </c>
-      <c r="L43" s="49">
+      <c r="L43" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M43" s="49">
         <v>6</v>
       </c>
-      <c r="M43" s="53">
+      <c r="N43" s="53">
         <v>1.2591000000000001</v>
       </c>
-      <c r="N43" s="53">
-        <f>M43*L43</f>
+      <c r="O43" s="53">
+        <f t="shared" si="4"/>
         <v>7.5546000000000006</v>
       </c>
-      <c r="O43" s="51"/>
-      <c r="P43" s="53"/>
-      <c r="T43" s="74"/>
-      <c r="W43" s="75"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="51"/>
+      <c r="Q43" s="53"/>
+      <c r="U43" s="65"/>
+      <c r="X43" s="66"/>
+    </row>
+    <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="38">
         <f>ROW(B44) - ROW($B$9)</f>
@@ -3623,25 +3734,29 @@
       <c r="K44" s="46">
         <v>1</v>
       </c>
-      <c r="L44" s="46">
+      <c r="L44" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M44" s="46">
         <v>6</v>
       </c>
-      <c r="M44" s="52">
+      <c r="N44" s="52">
         <v>2.9649999999999999</v>
       </c>
-      <c r="N44" s="52">
-        <f>M44*L44</f>
+      <c r="O44" s="52">
+        <f t="shared" si="4"/>
         <v>17.79</v>
       </c>
-      <c r="O44" s="48"/>
-      <c r="P44" s="52"/>
-      <c r="T44" s="74"/>
-      <c r="W44" s="75"/>
-    </row>
-    <row r="45" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P44" s="48"/>
+      <c r="Q44" s="52"/>
+      <c r="U44" s="65"/>
+      <c r="X44" s="66"/>
+    </row>
+    <row r="45" spans="1:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C45" s="59" t="s">
@@ -3656,10 +3771,12 @@
       <c r="F45" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="H45" s="49"/>
+      <c r="H45" s="49" t="s">
+        <v>194</v>
+      </c>
       <c r="I45" s="49" t="s">
         <v>194</v>
       </c>
@@ -3667,20 +3784,26 @@
       <c r="K45" s="49">
         <v>1</v>
       </c>
-      <c r="L45" s="49"/>
-      <c r="M45" s="53">
-        <v>0.08</v>
+      <c r="L45" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M45" s="49">
+        <v>6</v>
       </c>
       <c r="N45" s="53">
-        <f>M45*L45</f>
-        <v>0</v>
-      </c>
-      <c r="O45" s="71"/>
-      <c r="P45" s="53"/>
-      <c r="T45" s="74"/>
-      <c r="W45" s="75"/>
-    </row>
-    <row r="46" spans="1:23" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3.28</v>
+      </c>
+      <c r="O45" s="53">
+        <f t="shared" si="4"/>
+        <v>19.68</v>
+      </c>
+      <c r="P45" s="67"/>
+      <c r="Q45" s="53"/>
+      <c r="U45" s="65"/>
+      <c r="X45" s="66"/>
+    </row>
+    <row r="46" spans="1:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="38">
         <f>ROW(B46) - ROW($B$9)</f>
@@ -3713,25 +3836,29 @@
       <c r="K46" s="46">
         <v>1</v>
       </c>
-      <c r="L46" s="46">
+      <c r="L46" s="47">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M46" s="46">
         <v>10</v>
       </c>
-      <c r="M46" s="52">
+      <c r="N46" s="52">
         <v>0.19550000000000001</v>
       </c>
-      <c r="N46" s="52">
-        <f>M46*L46</f>
+      <c r="O46" s="52">
+        <f t="shared" si="4"/>
         <v>1.9550000000000001</v>
       </c>
-      <c r="O46" s="48"/>
-      <c r="P46" s="52"/>
-      <c r="T46" s="74"/>
-      <c r="W46" s="75"/>
-    </row>
-    <row r="47" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P46" s="48"/>
+      <c r="Q46" s="52"/>
+      <c r="U46" s="65"/>
+      <c r="X46" s="66"/>
+    </row>
+    <row r="47" spans="1:24" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C47" s="59" t="s">
@@ -3758,25 +3885,29 @@
       <c r="J47" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="K47" s="60">
+      <c r="K47" s="49">
         <v>1</v>
       </c>
-      <c r="L47" s="49">
+      <c r="L47" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M47" s="49">
         <v>10</v>
       </c>
-      <c r="M47" s="53">
+      <c r="N47" s="53">
         <v>0.15000000000000002</v>
       </c>
-      <c r="N47" s="53">
-        <f>M47*L47</f>
+      <c r="O47" s="53">
+        <f t="shared" si="4"/>
         <v>1.5000000000000002</v>
       </c>
-      <c r="O47" s="51"/>
-      <c r="P47" s="53"/>
-      <c r="T47" s="74"/>
-      <c r="W47" s="75"/>
-    </row>
-    <row r="48" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P47" s="51"/>
+      <c r="Q47" s="53"/>
+      <c r="U47" s="65"/>
+      <c r="X47" s="66"/>
+    </row>
+    <row r="48" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="33"/>
       <c r="C48" s="44"/>
@@ -3788,19 +3919,20 @@
       <c r="I48" s="37"/>
       <c r="J48" s="37"/>
       <c r="K48" s="37"/>
-      <c r="L48" s="84" t="s">
+      <c r="L48" s="37"/>
+      <c r="M48" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="M48" s="85"/>
-      <c r="N48" s="68">
-        <f>SUM(N10:N47)</f>
-        <v>194.26880000000003</v>
-      </c>
-      <c r="O48" s="80"/>
-      <c r="P48" s="81"/>
-      <c r="T48" s="74"/>
-    </row>
-    <row r="49" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="77"/>
+      <c r="O48" s="62">
+        <f>SUM(O10:O47)</f>
+        <v>243.8888</v>
+      </c>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="73"/>
+      <c r="U48" s="65"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="25"/>
       <c r="C49" s="45"/>
@@ -3812,28 +3944,29 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="84" t="s">
+      <c r="L49" s="10"/>
+      <c r="M49" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="M49" s="85"/>
-      <c r="N49" s="69">
-        <f>N48/5</f>
-        <v>38.853760000000008</v>
-      </c>
-      <c r="O49" s="82"/>
-      <c r="P49" s="83"/>
-      <c r="W49" s="75"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="M51" s="75"/>
+      <c r="N49" s="77"/>
+      <c r="O49" s="63">
+        <f>O48/5</f>
+        <v>48.777760000000001</v>
+      </c>
+      <c r="P49" s="74"/>
+      <c r="Q49" s="75"/>
+      <c r="X49" s="66"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="N51" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="P3:P8"/>
-    <mergeCell ref="O48:P49"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="Q3:Q8"/>
+    <mergeCell ref="P48:Q49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
